--- a/SGC-CKN/Excel/d8347323-2b43-4a94-8003-fc3931622e75_Lô_CT-02_P11-44_D800_14-04-2026.xlsx
+++ b/SGC-CKN/Excel/d8347323-2b43-4a94-8003-fc3931622e75_Lô_CT-02_P11-44_D800_14-04-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>14:00 14/04/2026</t>
+    <t>14:00 04/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>20:19 14/04/2026</t>
+    <t>20:19 04/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">14:00
-14/04/2026</t>
+04/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">14:30
-14/04/2026</t>
+04/04/2026</t>
   </si>
   <si>
     <t/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:00
-14/04/2026</t>
+04/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:20
-14/04/2026</t>
+04/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:40
-14/04/2026</t>
+04/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:50
-14/04/2026</t>
+04/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">16:00
-14/04/2026</t>
+04/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">16:20
-14/04/2026</t>
+04/04/2026</t>
   </si>
   <si>
     <t>cham soi</t>
@@ -179,7 +179,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:19
-14/04/2026</t>
+04/04/2026</t>
   </si>
   <si>
     <t>KT Khoan</t>

--- a/SGC-CKN/Excel/d8347323-2b43-4a94-8003-fc3931622e75_Lô_CT-02_P11-44_D800_14-04-2026.xlsx
+++ b/SGC-CKN/Excel/d8347323-2b43-4a94-8003-fc3931622e75_Lô_CT-02_P11-44_D800_14-04-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>14:00 04/04/2026</t>
+    <t>14:00 01/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>20:19 04/04/2026</t>
+    <t>20:19 01/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">14:00
-04/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">14:30
-04/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:00
-04/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:20
-04/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:40
-04/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:50
-04/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">16:00
-04/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">16:20
-04/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>cham soi</t>
@@ -179,7 +179,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:19
-04/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>KT Khoan</t>

--- a/SGC-CKN/Excel/d8347323-2b43-4a94-8003-fc3931622e75_Lô_CT-02_P11-44_D800_14-04-2026.xlsx
+++ b/SGC-CKN/Excel/d8347323-2b43-4a94-8003-fc3931622e75_Lô_CT-02_P11-44_D800_14-04-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>20:19 01/04/2026</t>
+    <t>20:14 01/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -178,7 +178,7 @@
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">20:19
+    <t xml:space="preserve">20:14
 01/04/2026</t>
   </si>
   <si>
@@ -1151,7 +1151,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="G11" s="5">
         <v>-3.8</v>
@@ -1160,10 +1160,10 @@
         <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J11" s="8">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1402,13 +1402,13 @@
         <v>-50.05</v>
       </c>
       <c r="H18" s="27">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="I18" s="27">
         <v>6.05</v>
       </c>
       <c r="J18" s="30">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="K18" s="28" t="s">
         <v>53</v>
@@ -1563,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="F2" s="5">
         <v>-3.8</v>
@@ -1572,10 +1572,10 @@
         <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="I2" s="8">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1772,13 +1772,13 @@
         <v>-50.05</v>
       </c>
       <c r="G9" s="27">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="H9" s="27">
         <v>6.05</v>
       </c>
       <c r="I9" s="30">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1795,19 +1795,19 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="F10" s="33">
         <v>-50.05</v>
       </c>
       <c r="G10" s="33">
-        <v>6.32</v>
+        <v>6.23</v>
       </c>
       <c r="H10" s="33">
-        <v>50.05</v>
+        <v>48.95</v>
       </c>
       <c r="I10" s="33">
-        <v>7.92</v>
+        <v>7.85</v>
       </c>
     </row>
   </sheetData>
